--- a/public/observations-summary.xlsx
+++ b/public/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="175">
   <si>
     <t>Profile</t>
   </si>
@@ -45,6 +45,498 @@
   </si>
   <si>
     <t>Method</t>
+  </si>
+  <si>
+    <t>pghd-activity</t>
+  </si>
+  <si>
+    <t>PGHD Activity Profile</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#activity</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-activity-codes (required)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>Quantityĵ</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>pghd-alchol-consumption</t>
+  </si>
+  <si>
+    <t>PGHD AlcholConsumption Profile</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#social-history</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-alchol-consumption-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-alchol-use</t>
+  </si>
+  <si>
+    <t>PGHD AlcholUse Profile</t>
+  </si>
+  <si>
+    <t>null#74013-4</t>
+  </si>
+  <si>
+    <t>pghd-audiogram</t>
+  </si>
+  <si>
+    <t>PGHD Audiogram Profile</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#exam</t>
+  </si>
+  <si>
+    <t>null#89015-2</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>pghd-blood-glucose</t>
+  </si>
+  <si>
+    <t>PGHD BloodGlucose Profile</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#vital-signs</t>
+  </si>
+  <si>
+    <t>null#bloodGlucose</t>
+  </si>
+  <si>
+    <t>pghd-bloodpressure</t>
+  </si>
+  <si>
+    <t>PGHD BloodPressure Profile</t>
+  </si>
+  <si>
+    <t>null#85354-9, null#bloodPressure</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-vital-signs-codes (required)</t>
+  </si>
+  <si>
+    <t>LOINC#8480-6, Observation PGHD Codes#bloodPressureSystolic</t>
+  </si>
+  <si>
+    <t>LOINC#8462-4, Observation PGHD Codes#bloodPressureDiastolic</t>
+  </si>
+  <si>
+    <t>pghd-bmi</t>
+  </si>
+  <si>
+    <t>PGHD BMI Profile</t>
+  </si>
+  <si>
+    <t>null#39156-5, null#bodyMassIndex</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-body-measurements-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-bodyheight</t>
+  </si>
+  <si>
+    <t>PGHD BodyHeight Profile</t>
+  </si>
+  <si>
+    <t>null#8302-2, null#height</t>
+  </si>
+  <si>
+    <t>pghd-bodymeasurement</t>
+  </si>
+  <si>
+    <t>PGHD Body Measurement Profile</t>
+  </si>
+  <si>
+    <t>pghd-bodytemperature</t>
+  </si>
+  <si>
+    <t>PGHD BodyTemperature Profile</t>
+  </si>
+  <si>
+    <t>null#8310-5, null#bodyTemperature</t>
+  </si>
+  <si>
+    <t>pghd-bodyweight</t>
+  </si>
+  <si>
+    <t>PGHD BodyWeight Profile</t>
+  </si>
+  <si>
+    <t>null#29463-7, null#bodyMass</t>
+  </si>
+  <si>
+    <t>pghd-cardiac-function</t>
+  </si>
+  <si>
+    <t>PGHD Cardiac Function Profile</t>
+  </si>
+  <si>
+    <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>pghd-diving</t>
+  </si>
+  <si>
+    <t>PGHD Diving Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-diving-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-electrocardiogram</t>
+  </si>
+  <si>
+    <t>PGHD Electrocardiogram Profile</t>
+  </si>
+  <si>
+    <t>ECG Classification Codes#classification</t>
+  </si>
+  <si>
+    <t>ECG Classification Codes#symptomsStatus</t>
+  </si>
+  <si>
+    <t>pghd-food</t>
+  </si>
+  <si>
+    <t>PGHD Food Profile</t>
+  </si>
+  <si>
+    <t>stringĵ</t>
+  </si>
+  <si>
+    <t>pghd-hearing</t>
+  </si>
+  <si>
+    <t>PGHD Hearing Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-hearing-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-hearing-sensitivity</t>
+  </si>
+  <si>
+    <t>PGHD HearingSensitivity Profile</t>
+  </si>
+  <si>
+    <t>Hearing Sensitivity Codes#frequency</t>
+  </si>
+  <si>
+    <t>Hearing Sensitivity Codes#leftEarSensitivity</t>
+  </si>
+  <si>
+    <t>Hearing Sensitivity Codes#rightEarSensitivity</t>
+  </si>
+  <si>
+    <t>pghd-heartbeat</t>
+  </si>
+  <si>
+    <t>PGHD Heartbeat Profile</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Observation PGHD Codes#heartBeatSeries</t>
+  </si>
+  <si>
+    <t>pghd-heartrate</t>
+  </si>
+  <si>
+    <t>PGHD HeartRate Profile</t>
+  </si>
+  <si>
+    <t>null#8867-4, null#heartRate</t>
+  </si>
+  <si>
+    <t>pghd-medication-adherence</t>
+  </si>
+  <si>
+    <t>PGHD Medication Adherence Profile</t>
+  </si>
+  <si>
+    <t>null#medicationAdherence</t>
+  </si>
+  <si>
+    <t>Periodĵ</t>
+  </si>
+  <si>
+    <t>pghd-mindfulness</t>
+  </si>
+  <si>
+    <t>PGHD Mindfulness Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-mindfulness-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-mobility</t>
+  </si>
+  <si>
+    <t>PGHD Mobility Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-mobility-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-nutrition</t>
+  </si>
+  <si>
+    <t>PGHD Nutrition Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-nutrition-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-observation-scored-assessment</t>
+  </si>
+  <si>
+    <t>PGHD Scored Assessment Profile</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#survey</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-mind-codes (required)</t>
+  </si>
+  <si>
+    <t>integerĵ</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>Scored Assessment Codes#gad7Risk</t>
+  </si>
+  <si>
+    <t>Scored Assessment Codes#phq9Risk</t>
+  </si>
+  <si>
+    <t>pghd-observation-state-of-mind</t>
+  </si>
+  <si>
+    <t>PGHD State of Mind Profile</t>
+  </si>
+  <si>
+    <t>State of Mind Codes#kind</t>
+  </si>
+  <si>
+    <t>State of Mind Codes#valence</t>
+  </si>
+  <si>
+    <t>State of Mind Codes#valenceClassification</t>
+  </si>
+  <si>
+    <t>State of Mind Codes#labels</t>
+  </si>
+  <si>
+    <t>State of Mind Codes#associations</t>
+  </si>
+  <si>
+    <t>pghd-oxygenSaturation</t>
+  </si>
+  <si>
+    <t>PGHD OxygenSaturation Profile</t>
+  </si>
+  <si>
+    <t>null#2708-6, null#oxygenSaturation</t>
+  </si>
+  <si>
+    <t>pghd-pregnancy-status</t>
+  </si>
+  <si>
+    <t>PGHD Pregnancy Status Profile</t>
+  </si>
+  <si>
+    <t>null#82810-3</t>
+  </si>
+  <si>
+    <t>pghd-reproductive-health</t>
+  </si>
+  <si>
+    <t>PGHD ReproductiveHealth Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-reproductive-health-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-respiratoryrate</t>
+  </si>
+  <si>
+    <t>PGHD RespiratoryRate Profile</t>
+  </si>
+  <si>
+    <t>null#9279-1, null#respiratoryRate</t>
+  </si>
+  <si>
+    <t>pghd-selfcare</t>
+  </si>
+  <si>
+    <t>PGHD Self Care Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-selfcare-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-sleep</t>
+  </si>
+  <si>
+    <t>PGHD Sleep Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-sleep-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-sleep-episode</t>
+  </si>
+  <si>
+    <t>PGHD Sleep Episode Profile</t>
+  </si>
+  <si>
+    <t>null#sleepEpisode</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#latencyToSleepOnset</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#latencyToArising</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#totalSleepTime</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#coreSleepDuration</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#coreSleepPercentage</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#deepSleepDuration</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#deepSleepPercentage</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#remSleepDuration</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#remSleepPercentage</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#wakeAfterSleepOnset</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#numberOfAwakenings</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#sleepEfficiencyPercentage</t>
+  </si>
+  <si>
+    <t>booleanĵ</t>
+  </si>
+  <si>
+    <t>Sleep Episode Codes#isMainSleep</t>
+  </si>
+  <si>
+    <t>pghd-snore-event</t>
+  </si>
+  <si>
+    <t>PGHD SnoreEvent Profile</t>
+  </si>
+  <si>
+    <t>null#snoreEvent</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>Snore Event Item Codes#snoreIntensity</t>
+  </si>
+  <si>
+    <t>Snore Event Item Codes#bodyPosture</t>
+  </si>
+  <si>
+    <t>pghd-snore-index</t>
+  </si>
+  <si>
+    <t>PGHD SnoreIndex Profile</t>
+  </si>
+  <si>
+    <t>null#snoreIndex</t>
+  </si>
+  <si>
+    <t>pghd-symptom</t>
+  </si>
+  <si>
+    <t>PGHD Symptom Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-symptom-snomedct-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-testresult</t>
+  </si>
+  <si>
+    <t>PGHD Test Result Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-lab-results-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-uvexposure</t>
+  </si>
+  <si>
+    <t>PGHD UVExposure Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-uvexposure-codes (required)</t>
+  </si>
+  <si>
+    <t>pghd-vitalsigns</t>
+  </si>
+  <si>
+    <t>PGHD Vital Signs Profile</t>
+  </si>
+  <si>
+    <t>pghd-voltage-measurement</t>
+  </si>
+  <si>
+    <t>PGHD VoltageMeasurement Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-ecg-lead-codes (required)</t>
+  </si>
+  <si>
+    <t>SampledDataĵ</t>
+  </si>
+  <si>
+    <t>pghd-workout</t>
+  </si>
+  <si>
+    <t>PGHD Workout Profile</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/ValueSet/observation-workout-codes (required)</t>
   </si>
 </sst>
 </file>
@@ -178,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -216,6 +708,2491 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
